--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -531,12 +531,8 @@
           <t>33.35</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>13.11</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>4.59</v>
-      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>综合评分78.0分（基本面100/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -589,12 +585,8 @@
           <t>58.24</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>6.62</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>1.04</v>
-      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>综合评分71.0分（基本面82.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -647,12 +639,8 @@
           <t>28.42</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>19.21</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>3.22</v>
-      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>综合评分70.0分（基本面78.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -705,12 +693,8 @@
           <t>351.00</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>19.11</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>4.36</v>
-      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>综合评分69.0分（基本面87.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -763,12 +747,8 @@
           <t>1330.00</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>20.42</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>6.62</v>
-      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分66.5分（基本面73.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -821,12 +801,8 @@
           <t>41.69</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>6.93</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>0.92</v>
-      </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>综合评分66.0分（基本面72.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>32.87</t>
         </is>
       </c>
       <c r="E2" s="2" t="n"/>
@@ -545,7 +545,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=52.7中性区</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=48.3中性区</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -582,14 +582,14 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>58.24</t>
+          <t>56.36</t>
         </is>
       </c>
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>综合评分71.0分（基本面82.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分72.0分（基本面82.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=84.9超买区，短期回调风险</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=73.7中性区</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -614,46 +614,50 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>基本面82.0 / 技术面60.0 / 综合71.0</t>
+          <t>基本面82.0 / 技术面62.0 / 综合72.0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>新能源电池</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28.42</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
+          <t>348.20</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>4.32</v>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>综合评分70.0分（基本面78.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分69.0分（基本面87.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=59.7中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=15.8超卖区</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -668,46 +672,46 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>基本面78.0 / 技术面62.0 / 综合70.0</t>
+          <t>基本面87.0 / 技术面51.0 / 综合69.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>新能源电池</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>351.00</t>
+          <t>41.07</t>
         </is>
       </c>
       <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分69.0分（基本面87.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.0分（基本面72.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=15.6超卖区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=74.6中性区</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -722,7 +726,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面87.0 / 技术面51.0 / 综合69.0</t>
+          <t>基本面72.0 / 技术面62.0 / 综合67.0</t>
         </is>
       </c>
     </row>
@@ -744,11 +748,15 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1330.00</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
+          <t>1316.01</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>6.55</v>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分66.5分（基本面73.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -761,7 +769,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=63.6中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=56.2中性区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -783,39 +791,39 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>27.85</t>
         </is>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>综合评分66.0分（基本面72.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分65.0分（基本面78.0/技术面52.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=84.0超买区，短期回调风险</t>
+          <t>趋势中性，观望。均线多头排列(5&gt;10&gt;20&gt;60)；MACD死叉；RSI=45.1中性区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -830,7 +838,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>基本面72.0 / 技术面60.0 / 综合66.0</t>
+          <t>基本面78.0 / 技术面52.0 / 综合65.0</t>
         </is>
       </c>
     </row>
@@ -852,18 +860,18 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>87.57</t>
+          <t>86.27</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>15.05</v>
+        <v>14.83</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>3.15</v>
+        <v>3.11</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分65.5分（基本面75.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分63.5分（基本面75.0/技术面52.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -873,7 +881,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=75.7超买区，短期回调风险</t>
+          <t>趋势中性，观望。均线多头排列(5&gt;10&gt;20&gt;60)；MACD死叉；RSI=63.5中性区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -888,7 +896,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面75.0 / 技术面56.0 / 综合65.5</t>
+          <t>基本面75.0 / 技术面52.0 / 综合63.5</t>
         </is>
       </c>
     </row>
@@ -910,7 +918,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -925,7 +933,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>综合评分53.5分（基本面60.0/技术面47.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
+          <t>综合评分55.5分（基本面60.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -935,7 +943,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=27.0超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=31.2超卖区</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -950,7 +958,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>基本面60.0 / 技术面47.0 / 综合53.5</t>
+          <t>基本面60.0 / 技术面51.0 / 综合55.5</t>
         </is>
       </c>
     </row>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -639,12 +639,8 @@
           <t>348.20</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>18.95</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>4.32</v>
-      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>综合评分69.0分（基本面87.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -751,12 +747,8 @@
           <t>1316.01</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>6.55</v>
-      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分66.5分（基本面73.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -863,12 +855,8 @@
           <t>86.27</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>14.83</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>3.11</v>
-      </c>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>综合评分63.5分（基本面75.0/技术面52.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -585,8 +585,12 @@
           <t>56.36</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
+      <c r="E3" s="2" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>1.01</v>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>综合评分72.0分（基本面82.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -747,8 +751,12 @@
           <t>1316.01</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
+      <c r="E6" s="2" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>6.55</v>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分66.5分（基本面73.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -585,12 +585,8 @@
           <t>56.36</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>1.01</v>
-      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>综合评分72.0分（基本面82.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -751,12 +747,8 @@
           <t>1316.01</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>6.55</v>
-      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分66.5分（基本面73.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -528,14 +528,14 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>32.87</t>
+          <t>33.86</t>
         </is>
       </c>
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>综合评分78.0分（基本面100/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分80.0分（基本面100/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -545,7 +545,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=48.3中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=59.4中性区</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -560,7 +560,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>基本面100 / 技术面56.0 / 综合78.0</t>
+          <t>基本面100 / 技术面60.0 / 综合80.0</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>56.36</t>
+          <t>55.70</t>
         </is>
       </c>
       <c r="E3" s="2" t="n"/>
@@ -599,7 +599,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=73.7中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=67.2中性区</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -621,39 +621,39 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>新能源电池</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>348.20</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>综合评分69.0分（基本面87.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分70.0分（基本面78.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=15.8超卖区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=39.0中性区</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -668,46 +668,50 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>基本面87.0 / 技术面51.0 / 综合69.0</t>
+          <t>基本面78.0 / 技术面62.0 / 综合70.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>新能源电池</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41.07</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
+          <t>335.49</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>4.16</v>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分67.0分（基本面72.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分68.5分（基本面87.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=74.6中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=14.7超卖区；近20日已跌-14.1%，接近超跌</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -722,51 +726,55 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面72.0 / 技术面62.0 / 综合67.0</t>
+          <t>基本面87.0 / 技术面50.0 / 综合68.5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>白酒</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1316.01</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
+          <t>40.90</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.9</v>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>综合评分66.5分（基本面73.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.0分（基本面72.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=16.75%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.30%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=56.2中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=67.6中性区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>归母净利润同比-1.95%，利润下滑需警惕；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -776,46 +784,46 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>基本面73.0 / 技术面60.0 / 综合66.5</t>
+          <t>基本面72.0 / 技术面62.0 / 综合67.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27.85</t>
+          <t>85.15</t>
         </is>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>综合评分65.0分（基本面78.0/技术面52.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分65.5分（基本面75.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。均线多头排列(5&gt;10&gt;20&gt;60)；MACD死叉；RSI=45.1中性区</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=52.2中性区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -830,51 +838,51 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>基本面78.0 / 技术面52.0 / 综合65.0</t>
+          <t>基本面75.0 / 技术面56.0 / 综合65.5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>白酒</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>86.27</t>
+          <t>1309.30</t>
         </is>
       </c>
       <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分63.5分（基本面75.0/技术面52.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分64.5分（基本面73.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=16.75%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.30%，保持正增长</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。均线多头排列(5&gt;10&gt;20&gt;60)；MACD死叉；RSI=63.5中性区</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=50.5中性区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>归母净利润同比-1.95%，利润下滑需警惕；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -884,7 +892,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面75.0 / 技术面52.0 / 综合63.5</t>
+          <t>基本面73.0 / 技术面56.0 / 综合64.5</t>
         </is>
       </c>
     </row>
@@ -906,7 +914,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -921,7 +929,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>综合评分55.5分（基本面60.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
+          <t>综合评分53.0分（基本面60.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -931,7 +939,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=31.2超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=44.7中性区</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -946,7 +954,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>基本面60.0 / 技术面51.0 / 综合55.5</t>
+          <t>基本面60.0 / 技术面46.0 / 综合53.0</t>
         </is>
       </c>
     </row>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -693,12 +693,8 @@
           <t>335.49</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>18.26</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>4.16</v>
-      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>综合评分68.5分（基本面87.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -751,12 +747,8 @@
           <t>40.90</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分67.0分（基本面72.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -809,8 +801,12 @@
           <t>85.15</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
+      <c r="E7" s="2" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>3.07</v>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>综合评分65.5分（基本面75.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -801,12 +801,8 @@
           <t>85.15</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>14.64</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>3.07</v>
-      </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>综合评分65.5分（基本面75.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -693,8 +693,12 @@
           <t>335.49</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
+      <c r="E5" s="2" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>4.16</v>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>综合评分68.5分（基本面87.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -801,8 +805,12 @@
           <t>85.15</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
+      <c r="E7" s="2" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>3.07</v>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>综合评分65.5分（基本面75.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -693,12 +693,8 @@
           <t>335.49</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>18.26</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>4.16</v>
-      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>综合评分68.5分（基本面87.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -805,12 +801,8 @@
           <t>85.15</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>14.64</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>3.07</v>
-      </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>综合评分65.5分（基本面75.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>33.86</t>
+          <t>34.40</t>
         </is>
       </c>
       <c r="E2" s="2" t="n"/>
@@ -545,7 +545,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=59.4中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=54.0中性区</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>55.70</t>
+          <t>56.26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n"/>
@@ -599,7 +599,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=67.2中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=68.7中性区</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -621,39 +621,39 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>新能源电池</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>336.84</t>
         </is>
       </c>
       <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>综合评分70.0分（基本面78.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分70.5分（基本面87.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=39.0中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=17.1超卖区；近20日已跌-14.5%，接近超跌</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -668,46 +668,46 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>基本面78.0 / 技术面62.0 / 综合70.0</t>
+          <t>基本面87.0 / 技术面54.0 / 综合70.5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>新能源电池</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>335.49</t>
+          <t>41.00</t>
         </is>
       </c>
       <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分68.5分（基本面87.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.0分（基本面72.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=14.7超卖区；近20日已跌-14.1%，接近超跌</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=72.4中性区</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -722,46 +722,46 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面87.0 / 技术面50.0 / 综合68.5</t>
+          <t>基本面72.0 / 技术面62.0 / 综合67.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40.90</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>综合评分67.0分（基本面72.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.0分（基本面78.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=67.6中性区</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=47.7中性区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>基本面72.0 / 技术面62.0 / 综合67.0</t>
+          <t>基本面78.0 / 技术面56.0 / 综合67.0</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85.15</t>
+          <t>86.02</t>
         </is>
       </c>
       <c r="E7" s="2" t="n"/>
@@ -815,7 +815,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=52.2中性区</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=53.1中性区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -837,44 +837,44 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>白酒</t>
+          <t>消费电子</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1309.30</t>
+          <t>55.86</t>
         </is>
       </c>
       <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分64.5分（基本面73.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分65.0分（基本面84.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=16.75%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.30%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=50.5中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=58.8中性区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>归母净利润同比-1.95%，利润下滑需警惕；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面73.0 / 技术面56.0 / 综合64.5</t>
+          <t>基本面84.0 / 技术面46.0 / 综合65.0</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=44.7中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=47.3中性区</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -528,14 +528,14 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>34.40</t>
+          <t>34.11</t>
         </is>
       </c>
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>综合评分80.0分（基本面100/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分83.0分（基本面100/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -545,7 +545,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=54.0中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=45.2中性区</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -560,46 +560,46 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>基本面100 / 技术面60.0 / 综合80.0</t>
+          <t>基本面100 / 技术面66.0 / 综合83.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>新能源电池</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>56.26</t>
+          <t>338.06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>综合评分72.0分（基本面82.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分70.5分（基本面87.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=68.7中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=11.1超卖区；近20日已跌-14.7%，接近超跌</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -614,46 +614,46 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>基本面82.0 / 技术面62.0 / 综合72.0</t>
+          <t>基本面87.0 / 技术面54.0 / 综合70.5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>新能源电池</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>336.84</t>
+          <t>28.09</t>
         </is>
       </c>
       <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>综合评分70.5分（基本面87.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分69.0分（基本面78.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=17.1超卖区；近20日已跌-14.5%，接近超跌</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=52.9中性区</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -668,51 +668,51 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>基本面87.0 / 技术面54.0 / 综合70.5</t>
+          <t>基本面78.0 / 技术面60.0 / 综合69.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>白酒</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41.00</t>
+          <t>1285.13</t>
         </is>
       </c>
       <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分67.0分（基本面72.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.5分（基本面73.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=16.75%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.30%，保持正增长</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=72.4中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=54.7中性区</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>归母净利润同比-1.95%，利润下滑需警惕；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -722,46 +722,46 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面72.0 / 技术面62.0 / 综合67.0</t>
+          <t>基本面73.0 / 技术面62.0 / 综合67.5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>综合评分67.0分（基本面78.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分66.0分（基本面72.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=47.7中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=75.1超买区，短期回调风险</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>基本面78.0 / 技术面56.0 / 综合67.0</t>
+          <t>基本面72.0 / 技术面60.0 / 综合66.0</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86.02</t>
+          <t>86.20</t>
         </is>
       </c>
       <c r="E7" s="2" t="n"/>
@@ -815,7 +815,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=53.1中性区</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=60.3中性区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -837,44 +837,44 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>消费电子</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>55.86</t>
+          <t>55.52</t>
         </is>
       </c>
       <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分65.0分（基本面84.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分64.0分（基本面82.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=58.8中性区</t>
+          <t>趋势中性，观望。价格站上60日均线；MACD死叉；RSI=60.3中性区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面84.0 / 技术面46.0 / 综合65.0</t>
+          <t>基本面82.0 / 技术面46.0 / 综合64.0</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=47.3中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=39.5中性区</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -675,44 +675,44 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>白酒</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1285.13</t>
+          <t>55.52</t>
         </is>
       </c>
       <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分67.5分（基本面73.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分69.0分（基本面82.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=16.75%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.30%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=54.7中性区</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=65.7中性区</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>归母净利润同比-1.95%，利润下滑需警惕；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -722,51 +722,51 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面73.0 / 技术面62.0 / 综合67.5</t>
+          <t>基本面82.0 / 技术面56.0 / 综合69.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>白酒</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>1285.13</t>
         </is>
       </c>
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>综合评分66.0分（基本面72.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.5分（基本面73.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=16.75%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.30%，保持正增长</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=75.1超买区，短期回调风险</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=54.7中性区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>归母净利润同比-1.95%，利润下滑需警惕；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -776,46 +776,46 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>基本面72.0 / 技术面60.0 / 综合66.0</t>
+          <t>基本面73.0 / 技术面62.0 / 综合67.5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86.20</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>综合评分65.5分（基本面75.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分66.0分（基本面72.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=60.3中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=75.1超买区，短期回调风险</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -830,46 +830,46 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>基本面75.0 / 技术面56.0 / 综合65.5</t>
+          <t>基本面72.0 / 技术面60.0 / 综合66.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>55.52</t>
+          <t>86.20</t>
         </is>
       </c>
       <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分64.0分（基本面82.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分65.5分（基本面75.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；MACD死叉；RSI=60.3中性区</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=60.3中性区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面82.0 / 技术面46.0 / 综合64.0</t>
+          <t>基本面75.0 / 技术面56.0 / 综合65.5</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>综合评分53.0分（基本面60.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
+          <t>综合评分51.0分（基本面60.0/技术面42.0），技术面趋势偏弱，回避或减仓; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=39.5中性区</t>
+          <t>趋势偏弱，回避或减仓。价格位于60日均线下方，中期趋势偏弱；RSI=39.1中性区</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>基本面60.0 / 技术面46.0 / 综合53.0</t>
+          <t>基本面60.0 / 技术面42.0 / 综合51.0</t>
         </is>
       </c>
     </row>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -747,8 +747,12 @@
           <t>1285.13</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
+      <c r="E6" s="2" t="n">
+        <v>19.73</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>6.39</v>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分67.5分（基本面73.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -747,12 +747,8 @@
           <t>1285.13</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>19.73</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>6.39</v>
-      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分67.5分（基本面73.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -528,14 +528,14 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>34.11</t>
+          <t>31.89</t>
         </is>
       </c>
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>综合评分83.0分（基本面100/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分80.5分（基本面100/技术面61.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -545,7 +545,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=45.2中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；RSI=34.5超卖区</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -560,7 +560,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>基本面100 / 技术面66.0 / 综合83.0</t>
+          <t>基本面100 / 技术面61.0 / 综合80.5</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>338.06</t>
+          <t>330.70</t>
         </is>
       </c>
       <c r="E3" s="2" t="n"/>
@@ -599,7 +599,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=11.1超卖区；近20日已跌-14.7%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=10.4超卖区；近20日已跌-16.1%，接近超跌</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28.09</t>
+          <t>28.24</t>
         </is>
       </c>
       <c r="E4" s="2" t="n"/>
@@ -653,7 +653,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=52.9中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=52.0中性区</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -675,39 +675,39 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>55.52</t>
+          <t>86.24</t>
         </is>
       </c>
       <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分69.0分（基本面82.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.5分（基本面75.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=65.7中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=51.6中性区</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -722,51 +722,51 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面82.0 / 技术面56.0 / 综合69.0</t>
+          <t>基本面75.0 / 技术面60.0 / 综合67.5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>白酒</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1285.13</t>
+          <t>41.20</t>
         </is>
       </c>
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>综合评分67.5分（基本面73.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.0分（基本面72.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=16.75%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.30%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=54.7中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=66.2中性区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>归母净利润同比-1.95%，利润下滑需警惕；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -776,46 +776,46 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>基本面73.0 / 技术面62.0 / 综合67.5</t>
+          <t>基本面72.0 / 技术面62.0 / 综合67.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>54.54</t>
         </is>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>综合评分66.0分（基本面72.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分64.0分（基本面82.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=75.1超买区，短期回调风险</t>
+          <t>趋势中性，观望。价格站上60日均线；MACD死叉；RSI=53.2中性区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -830,51 +830,51 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>基本面72.0 / 技术面60.0 / 综合66.0</t>
+          <t>基本面82.0 / 技术面46.0 / 综合64.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>消费电子</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>86.20</t>
+          <t>54.46</t>
         </is>
       </c>
       <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分65.5分（基本面75.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分63.0分（基本面84.0/技术面42.0），技术面趋势偏弱，回避或减仓; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=60.3中性区</t>
+          <t>趋势偏弱，回避或减仓。价格位于60日均线下方，中期趋势偏弱；RSI=52.8中性区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面75.0 / 技术面56.0 / 综合65.5</t>
+          <t>基本面84.0 / 技术面42.0 / 综合63.0</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势偏弱，回避或减仓。价格位于60日均线下方，中期趋势偏弱；RSI=39.1中性区</t>
+          <t>趋势偏弱，回避或减仓。价格位于60日均线下方，中期趋势偏弱；RSI=38.6中性区</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -528,14 +528,14 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>32.22</t>
         </is>
       </c>
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>综合评分80.5分（基本面100/技术面61.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分78.0分（基本面100/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -545,7 +545,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；RSI=34.5超卖区</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=35.9中性区</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -560,7 +560,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>基本面100 / 技术面61.0 / 综合80.5</t>
+          <t>基本面100 / 技术面56.0 / 综合78.0</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28.24</t>
+          <t>28.52</t>
         </is>
       </c>
       <c r="E4" s="2" t="n"/>
@@ -653,7 +653,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=52.0中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=57.4中性区</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86.24</t>
+          <t>86.79</t>
         </is>
       </c>
       <c r="E5" s="2" t="n"/>
@@ -707,7 +707,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=51.6中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=54.9中性区</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>54.54</t>
+          <t>55.15</t>
         </is>
       </c>
       <c r="E7" s="2" t="n"/>
@@ -815,7 +815,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；MACD死叉；RSI=53.2中性区</t>
+          <t>趋势中性，观望。价格站上60日均线；MACD死叉；RSI=56.8中性区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势偏弱，回避或减仓。价格位于60日均线下方，中期趋势偏弱；RSI=38.6中性区</t>
+          <t>趋势偏弱，回避或减仓。价格位于60日均线下方，中期趋势偏弱；RSI=38.8中性区</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -531,8 +531,12 @@
           <t>32.22</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
+      <c r="E2" s="2" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>4.44</v>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>综合评分78.0分（基本面100/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -639,8 +643,12 @@
           <t>28.52</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
+      <c r="E4" s="2" t="n">
+        <v>19.23</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>3.22</v>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>综合评分69.0分（基本面78.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -693,8 +701,12 @@
           <t>86.79</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
+      <c r="E5" s="2" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>3.11</v>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>综合评分67.5分（基本面75.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -747,8 +759,12 @@
           <t>41.20</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
+      <c r="E6" s="2" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.91</v>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分67.0分（基本面72.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -528,15 +528,11 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>32.22</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>12.68</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>4.44</v>
-      </c>
+          <t>32.26</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>综合评分78.0分（基本面100/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -549,7 +545,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=35.9中性区</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=36.1中性区</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -586,7 +582,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>330.70</t>
+          <t>330.51</t>
         </is>
       </c>
       <c r="E3" s="2" t="n"/>
@@ -640,15 +636,11 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28.52</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>19.23</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>3.22</v>
-      </c>
+          <t>28.45</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>综合评分69.0分（基本面78.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -661,7 +653,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=57.4中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=56.2中性区</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -698,15 +690,11 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86.79</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>14.83</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>3.11</v>
-      </c>
+          <t>86.26</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>综合评分67.5分（基本面75.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -719,7 +707,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=54.9中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=51.8中性区</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -756,15 +744,11 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>41.20</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>6.87</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.91</v>
-      </c>
+          <t>41.35</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分67.0分（基本面72.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -777,7 +761,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=66.2中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=68.2中性区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -799,44 +783,44 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>消费电子</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>55.15</t>
+          <t>55.39</t>
         </is>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>综合评分64.0分（基本面82.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分65.0分（基本面84.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；MACD死叉；RSI=56.8中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=55.8中性区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -846,51 +830,51 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>基本面82.0 / 技术面46.0 / 综合64.0</t>
+          <t>基本面84.0 / 技术面46.0 / 综合65.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>消费电子</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>54.46</t>
+          <t>54.83</t>
         </is>
       </c>
       <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分63.0分（基本面84.0/技术面42.0），技术面趋势偏弱，回避或减仓; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分64.0分（基本面82.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势偏弱，回避或减仓。价格位于60日均线下方，中期趋势偏弱；RSI=52.8中性区</t>
+          <t>趋势中性，观望。价格站上60日均线；MACD死叉；RSI=54.9中性区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -900,7 +884,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面84.0 / 技术面42.0 / 综合63.0</t>
+          <t>基本面82.0 / 技术面46.0 / 综合64.0</t>
         </is>
       </c>
     </row>
@@ -922,7 +906,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -947,7 +931,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势偏弱，回避或减仓。价格位于60日均线下方，中期趋势偏弱；RSI=38.8中性区</t>
+          <t>趋势偏弱，回避或减仓。价格位于60日均线下方，中期趋势偏弱；RSI=41.2中性区</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
